--- a/tech_tree_ru.xlsx
+++ b/tech_tree_ru.xlsx
@@ -8,23 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\step2\Desktop\Biome Weaver Dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CCB2AB6-6ADB-4035-B7E6-244CF8DAFF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1434E692-B46C-4DA3-9FBA-A9E721130EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Дерево улучшений" sheetId="1" r:id="rId1"/>
     <sheet name="Здания" sheetId="2" r:id="rId2"/>
     <sheet name="Предметы" sheetId="3" r:id="rId3"/>
     <sheet name="Рецепты" sheetId="4" r:id="rId4"/>
-    <sheet name="Найденные баги" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="317">
   <si>
     <t>Уровень</t>
   </si>
@@ -80,9 +79,6 @@
     <t>Рецепты Iron Ingot, Cooper Ingot (после починки)</t>
   </si>
   <si>
-    <t>УЖЕ ЕСТЬ (нужна починка привязки здания)</t>
-  </si>
-  <si>
     <t>research_mechanical_engineering</t>
   </si>
   <si>
@@ -239,9 +235,6 @@
     <t>Assembler (Сборщик)</t>
   </si>
   <si>
-    <t>Крафтит предметы из ресурсов (2 входа)</t>
-  </si>
-  <si>
     <t>smelter</t>
   </si>
   <si>
@@ -263,9 +256,6 @@
     <t>Constructor (Конструктор)</t>
   </si>
   <si>
-    <t>Быстрый крафт с одним входом (стержни, пластины, шестерни, провод)</t>
-  </si>
-  <si>
     <t>Дешевле и быстрее Assembler для простых рецептов с 1 входом</t>
   </si>
   <si>
@@ -725,9 +715,6 @@
     <t>recipe_plank</t>
   </si>
   <si>
-    <t>Вручную / Assembler</t>
-  </si>
-  <si>
     <t>1x Бревно</t>
   </si>
   <si>
@@ -737,15 +724,9 @@
     <t>УЖЕ ЕСТЬ (почин.)</t>
   </si>
   <si>
-    <t>plankRecipe_1 сейчас дублирует IronIngotRecipe по ошибке — нужно исправить на Log-&gt;Plank</t>
-  </si>
-  <si>
     <t>recipe_stone_brick</t>
   </si>
   <si>
-    <t>Вручную</t>
-  </si>
-  <si>
     <t>2x Камень</t>
   </si>
   <si>
@@ -764,9 +745,6 @@
     <t>1x Железный слиток</t>
   </si>
   <si>
-    <t>requiredBuilding сейчас пустое; нужно привязать к Smelter</t>
-  </si>
-  <si>
     <t>recipe_cooper_ingot</t>
   </si>
   <si>
@@ -776,9 +754,6 @@
     <t>1x Медный слиток</t>
   </si>
   <si>
-    <t>CooperIngotRecipe_1 сейчас скопирован из Iron-рецепта (id/название/входы); нужно исправить</t>
-  </si>
-  <si>
     <t>recipe_iron_rod</t>
   </si>
   <si>
@@ -833,9 +808,6 @@
     <t>Assembler</t>
   </si>
   <si>
-    <t>2x Доска + 4x Провод</t>
-  </si>
-  <si>
     <t>1x Плата</t>
   </si>
   <si>
@@ -977,56 +949,38 @@
     <t>Предлагаемый финальный крафт-предмет (условие победы)</t>
   </si>
   <si>
-    <t>Файл</t>
-  </si>
-  <si>
-    <t>Проблема</t>
-  </si>
-  <si>
-    <t>Что нужно исправить</t>
-  </si>
-  <si>
-    <t>CooperIngotRecipe_1.asset</t>
-  </si>
-  <si>
-    <t>id/displayName стоят 'recipe_iron_ingot'/'Iron Ingot' (скопировано с Iron-рецепта); входы/выходы тоже указывают на guid железной руды/слитка</t>
-  </si>
-  <si>
-    <t>Указать id=recipe_cooper_ingot, displayName=Copper Ingot, входы=1x Медная руда, выходы=1x Медный слиток, requiredBuilding=Smelter</t>
-  </si>
-  <si>
-    <t>plankRecipe_1.asset</t>
-  </si>
-  <si>
-    <t>id/displayName стоят 'recipe_iron_ingot'/'Iron Ingot' (скопировано); входы указывают на guid iron_ore вместо log</t>
-  </si>
-  <si>
-    <t>Указать id=recipe_plank, displayName=Plank, входы=1x Бревно, выходы=2x Доска</t>
-  </si>
-  <si>
-    <t>IronIngotRecipe.asset</t>
-  </si>
-  <si>
-    <t>requiredBuilding пустое (fileID: 0) — сейчас у рецепта нет привязки к зданию</t>
-  </si>
-  <si>
-    <t>Привязать requiredBuilding к новому зданию Smelter</t>
-  </si>
-  <si>
-    <t>Coope_rore.asset / Cooper_Ingot.asset</t>
-  </si>
-  <si>
-    <t>поля id стоят 'coope_rore' / 'cooper_Ingot' — несогласованное написание/регистр относительно остальных id (snake_case, 'copper')</t>
-  </si>
-  <si>
-    <t>Рассмотреть переименование id в copper_ore / copper_ingot для единообразия (только если ни один другой ассет не ссылается на старые id-строки, а не GUID)</t>
+    <t>silicon</t>
+  </si>
+  <si>
+    <t>кремний</t>
+  </si>
+  <si>
+    <t>Silicon</t>
+  </si>
+  <si>
+    <t>1x Кремний</t>
+  </si>
+  <si>
+    <t>Кремний</t>
+  </si>
+  <si>
+    <t>нет</t>
+  </si>
+  <si>
+    <t>Крафтит предметы из ресурсов (1 вход)</t>
+  </si>
+  <si>
+    <t>Быстрый крафт с двумя входами (стержни, пластины, шестерни, провод)</t>
+  </si>
+  <si>
+    <t>2x кремний + 4x Провод</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1044,8 +998,21 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1104,17 +1071,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1146,7 +1121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1208,23 +1183,79 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1608,8 +1639,8 @@
       <c r="G3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>18</v>
+      <c r="H3" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1617,25 +1648,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>24</v>
+      <c r="H4" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
@@ -1643,25 +1674,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="F5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="G5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>24</v>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1669,25 +1700,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="12" t="s">
+      <c r="F6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="12" t="s">
-        <v>34</v>
-      </c>
       <c r="H6" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
@@ -1695,25 +1726,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="F7" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="G7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="14" t="s">
-        <v>39</v>
-      </c>
       <c r="H7" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
@@ -1721,25 +1752,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="D8" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="16" t="s">
+      <c r="F8" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="G8" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="16" t="s">
-        <v>44</v>
-      </c>
       <c r="H8" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
@@ -1747,25 +1778,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="D9" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="18" t="s">
+      <c r="F9" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="G9" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G9" s="18" t="s">
-        <v>49</v>
-      </c>
       <c r="H9" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1791,42 +1822,42 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>57</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>58</v>
       </c>
       <c r="D2" s="19">
         <v>0</v>
@@ -1835,27 +1866,27 @@
         <v>8</v>
       </c>
       <c r="F2" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="H2" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="20" t="s">
         <v>60</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>63</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>64</v>
       </c>
       <c r="D3" s="19">
         <v>0</v>
@@ -1864,27 +1895,27 @@
         <v>8</v>
       </c>
       <c r="F3" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="H3" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="20" t="s">
         <v>60</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="C4" s="20" t="s">
         <v>66</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>67</v>
       </c>
       <c r="D4" s="19">
         <v>0</v>
@@ -1893,27 +1924,27 @@
         <v>8</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="20" t="s">
         <v>60</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>71</v>
+      <c r="C5" s="29" t="s">
+        <v>314</v>
       </c>
       <c r="D5" s="19">
         <v>1</v>
@@ -1922,27 +1953,27 @@
         <v>13</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G5" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="20" t="s">
         <v>60</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>74</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1951,451 +1982,451 @@
         <v>13</v>
       </c>
       <c r="F6" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>79</v>
+      <c r="C7" s="29" t="s">
+        <v>315</v>
       </c>
       <c r="D7" s="19">
         <v>2</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>24</v>
+      <c r="H7" s="33" t="s">
+        <v>12</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D8" s="19">
         <v>3</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="22" t="s">
-        <v>24</v>
+      <c r="H8" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D9" s="19">
         <v>3</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>24</v>
+      <c r="H9" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D10" s="19">
         <v>3</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="H10" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D11" s="19">
         <v>4</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="22" t="s">
-        <v>24</v>
+        <v>59</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D12" s="19">
         <v>4</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>24</v>
+      <c r="H12" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D13" s="19">
         <v>5</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D14" s="19">
         <v>5</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="H14" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D15" s="19">
         <v>5</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>24</v>
+        <v>59</v>
+      </c>
+      <c r="H15" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D16" s="19">
         <v>5</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F16" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="22" t="s">
-        <v>24</v>
+      <c r="H16" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D17" s="19">
         <v>5</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D18" s="19">
         <v>6</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>24</v>
+        <v>59</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D19" s="19">
         <v>6</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>24</v>
+        <v>59</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I19" s="20" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D20" s="19">
         <v>7</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="H20" s="22" t="s">
-        <v>24</v>
+        <v>59</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I20" s="20" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D21" s="19">
         <v>7</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="22" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="H21" s="35" t="s">
+        <v>23</v>
       </c>
       <c r="I21" s="20" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2405,7 +2436,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2419,39 +2450,39 @@
   <sheetData>
     <row r="1" spans="1:8" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -2460,7 +2491,7 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -2469,13 +2500,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -2484,7 +2515,7 @@
         <v>100</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>12</v>
@@ -2493,13 +2524,13 @@
     </row>
     <row r="4" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -2508,24 +2539,24 @@
         <v>100</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -2534,7 +2565,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>12</v>
@@ -2543,13 +2574,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -2558,7 +2589,7 @@
         <v>100</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>12</v>
@@ -2567,13 +2598,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -2582,7 +2613,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>12</v>
@@ -2591,13 +2622,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -2606,24 +2637,24 @@
         <v>100</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2632,7 +2663,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>12</v>
@@ -2641,13 +2672,13 @@
     </row>
     <row r="10" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2656,24 +2687,24 @@
         <v>100</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>169</v>
       </c>
       <c r="D11" s="7">
         <v>2</v>
@@ -2682,22 +2713,22 @@
         <v>100</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D12" s="7">
         <v>2</v>
@@ -2706,22 +2737,22 @@
         <v>100</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D13" s="7">
         <v>2</v>
@@ -2730,22 +2761,22 @@
         <v>100</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D14" s="7">
         <v>2</v>
@@ -2754,22 +2785,22 @@
         <v>100</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>176</v>
+      <c r="A15" s="21" t="s">
+        <v>173</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D15" s="7">
         <v>2</v>
@@ -2778,22 +2809,22 @@
         <v>100</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D16" s="9">
         <v>3</v>
@@ -2802,24 +2833,24 @@
         <v>100</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>158</v>
+        <v>179</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>155</v>
       </c>
       <c r="D17" s="9">
         <v>3</v>
@@ -2828,22 +2859,22 @@
         <v>100</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>184</v>
+      <c r="A18" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>312</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="D18" s="9">
         <v>3</v>
@@ -2851,47 +2882,47 @@
       <c r="E18" s="9">
         <v>100</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>24</v>
+      <c r="F18" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="D19" s="11">
-        <v>4</v>
-      </c>
-      <c r="E19" s="11">
+      <c r="A19" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="27">
+        <v>3</v>
+      </c>
+      <c r="E19" s="27">
         <v>100</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="12"/>
+      <c r="F19" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="28"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="D20" s="11">
         <v>4</v>
@@ -2900,22 +2931,22 @@
         <v>100</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D21" s="11">
         <v>4</v>
@@ -2924,22 +2955,22 @@
         <v>100</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H21" s="12"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D22" s="11">
         <v>4</v>
@@ -2948,48 +2979,46 @@
         <v>100</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H22" s="12"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="D23" s="13">
-        <v>5</v>
-      </c>
-      <c r="E23" s="13">
-        <v>500</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>196</v>
-      </c>
+      <c r="A23" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="11">
+        <v>4</v>
+      </c>
+      <c r="E23" s="11">
+        <v>100</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="12"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D24" s="13">
         <v>5</v>
@@ -2998,50 +3027,50 @@
         <v>500</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="D25" s="13">
         <v>5</v>
       </c>
       <c r="E25" s="13">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="D26" s="13">
         <v>5</v>
@@ -3050,22 +3079,24 @@
         <v>100</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="14"/>
+        <v>23</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D27" s="13">
         <v>5</v>
@@ -3074,70 +3105,70 @@
         <v>100</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H27" s="14"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="D28" s="13">
         <v>5</v>
       </c>
       <c r="E28" s="13">
+        <v>100</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="13">
+        <v>5</v>
+      </c>
+      <c r="E29" s="13">
         <v>500</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="14"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="D29" s="15">
-        <v>6</v>
-      </c>
-      <c r="E29" s="15">
-        <v>100</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="H29" s="16"/>
+      <c r="F29" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="14"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D30" s="15">
         <v>6</v>
@@ -3146,22 +3177,22 @@
         <v>100</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D31" s="15">
         <v>6</v>
@@ -3170,22 +3201,22 @@
         <v>100</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D32" s="15">
         <v>6</v>
@@ -3194,46 +3225,46 @@
         <v>100</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H32" s="16"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="D33" s="17">
-        <v>7</v>
-      </c>
-      <c r="E33" s="17">
+      <c r="A33" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="D33" s="15">
+        <v>6</v>
+      </c>
+      <c r="E33" s="15">
         <v>100</v>
       </c>
-      <c r="F33" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H33" s="18"/>
+      <c r="F33" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D34" s="17">
         <v>7</v>
@@ -3242,47 +3273,76 @@
         <v>100</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H34" s="18"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D35" s="17">
         <v>7</v>
       </c>
       <c r="E35" s="17">
+        <v>100</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="18"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D36" s="17">
+        <v>7</v>
+      </c>
+      <c r="E36" s="17">
         <v>50</v>
       </c>
-      <c r="F35" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>226</v>
+      <c r="F36" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G2:G36">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="УЖЕ ЕСТЬ">
+      <formula>NOT(ISERROR(SEARCH("УЖЕ ЕСТЬ",G2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3298,25 +3358,25 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -3325,27 +3385,27 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>233</v>
+        <v>154</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G2" s="2">
         <v>1</v>
@@ -3354,30 +3414,28 @@
         <v>8</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>237</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>239</v>
+        <v>157</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G3" s="2">
         <v>1</v>
@@ -3385,29 +3443,29 @@
       <c r="H3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
+      <c r="I3" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="G4" s="4">
         <v>0.5</v>
@@ -3416,30 +3474,28 @@
         <v>13</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G5" s="4">
         <v>1</v>
@@ -3448,714 +3504,679 @@
         <v>13</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>250</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>22</v>
+      <c r="A6" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>260</v>
       </c>
       <c r="D6" s="7">
         <v>2</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G6" s="7">
         <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>22</v>
+        <v>245</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>260</v>
       </c>
       <c r="D7" s="7">
         <v>2</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="G7" s="7">
         <v>1.5</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>22</v>
+        <v>248</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>260</v>
       </c>
       <c r="D8" s="7">
         <v>2</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G8" s="7">
         <v>1</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>22</v>
+        <v>251</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>260</v>
       </c>
       <c r="D9" s="7">
         <v>2</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="G9" s="7">
         <v>1</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>22</v>
+        <v>253</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>260</v>
       </c>
       <c r="D10" s="7">
         <v>2</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="G10" s="7">
         <v>1.5</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D11" s="9">
         <v>3</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>265</v>
+      <c r="E11" s="25" t="s">
+        <v>257</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G11" s="9">
         <v>2</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="9" t="s">
+      <c r="H11" s="22" t="s">
         <v>24</v>
       </c>
+      <c r="I11" s="6" t="s">
+        <v>232</v>
+      </c>
       <c r="J11" s="10"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>268</v>
+      <c r="A12" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>310</v>
       </c>
       <c r="D12" s="9">
         <v>3</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>270</v>
+        <v>257</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>311</v>
       </c>
       <c r="G12" s="9">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="9">
+        <v>3</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="G13" s="9">
         <v>2</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="10"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="D13" s="11">
-        <v>4</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="G13" s="11">
-        <v>3</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="12"/>
+      <c r="I13" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="J13" s="10"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>190</v>
+        <v>262</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>183</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>22</v>
+        <v>237</v>
       </c>
       <c r="D14" s="11">
         <v>4</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="G14" s="11">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J14" s="12"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>277</v>
+        <v>21</v>
       </c>
       <c r="D15" s="11">
         <v>4</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="G15" s="11">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J15" s="12"/>
     </row>
-    <row r="16" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="D16" s="11">
         <v>4</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="G16" s="11">
+        <v>2</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="12"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D17" s="11">
         <v>4</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="D17" s="13">
-        <v>5</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="G17" s="13">
-        <v>6</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="14"/>
+      <c r="E17" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="G17" s="11">
+        <v>4</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="12"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D18" s="13">
         <v>5</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="G18" s="13">
         <v>6</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>209</v>
+        <v>278</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>204</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D19" s="13">
         <v>5</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="G19" s="13">
+        <v>6</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D20" s="13">
+        <v>5</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="G20" s="13">
         <v>4</v>
       </c>
-      <c r="H19" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="14"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>292</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="D20" s="15">
-        <v>6</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="G20" s="15">
-        <v>5</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="16"/>
+      <c r="H20" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" s="14"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="D21" s="15">
         <v>6</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="G21" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J21" s="16"/>
     </row>
-    <row r="22" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="D22" s="15">
         <v>6</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="G22" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J22" s="16"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D23" s="15">
         <v>6</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="G23" s="15">
         <v>6</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J23" s="16"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="D24" s="17">
-        <v>7</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="G24" s="17">
-        <v>4</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="D24" s="15">
+        <v>6</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="G24" s="15">
+        <v>6</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="16"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D25" s="17">
         <v>7</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="G25" s="17">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J25" s="18"/>
     </row>
     <row r="26" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="D26" s="17">
         <v>7</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="G26" s="17">
+        <v>10</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="D27" s="17">
+        <v>7</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="G27" s="17">
         <v>15</v>
       </c>
-      <c r="H26" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>316</v>
+      <c r="H27" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I2:I27">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="УЖЕ ЕСТЬ">
+      <formula>NOT(ISERROR(SEARCH("УЖЕ ЕСТЬ",I2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="3" width="58" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>321</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>324</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>331</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>